--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/97.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/97.xlsx
@@ -426,13 +426,13 @@
         <v>-13.9025340399043</v>
       </c>
       <c r="E2">
-        <v>-28.77286173005325</v>
+        <v>-23.32065148040226</v>
       </c>
       <c r="F2">
-        <v>-3.367441659704846</v>
+        <v>-3.44207380096993</v>
       </c>
       <c r="G2">
-        <v>-20.44829413072222</v>
+        <v>-18.64768510136709</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-12.820942705994</v>
       </c>
       <c r="E3">
-        <v>-29.26269770651494</v>
+        <v>-21.89446293337458</v>
       </c>
       <c r="F3">
-        <v>-3.508809584540633</v>
+        <v>-3.644632954966466</v>
       </c>
       <c r="G3">
-        <v>-20.20096161821051</v>
+        <v>-16.09759173573973</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-11.7005996470809</v>
       </c>
       <c r="E4">
-        <v>-29.58162680969014</v>
+        <v>-24.63039484679672</v>
       </c>
       <c r="F4">
-        <v>-3.782231659723507</v>
+        <v>-3.607070618064073</v>
       </c>
       <c r="G4">
-        <v>-18.95224370407065</v>
+        <v>-17.46659997732177</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-10.69663246468016</v>
       </c>
       <c r="E5">
-        <v>-30.0328326386294</v>
+        <v>-23.98555826200048</v>
       </c>
       <c r="F5">
-        <v>-3.768407490787636</v>
+        <v>-3.242919614691588</v>
       </c>
       <c r="G5">
-        <v>-19.33991024199208</v>
+        <v>-17.28501655449275</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-9.782963528256248</v>
       </c>
       <c r="E6">
-        <v>-30.98198946945208</v>
+        <v>-25.97620750866226</v>
       </c>
       <c r="F6">
-        <v>-3.329477061499932</v>
+        <v>-3.936684954685612</v>
       </c>
       <c r="G6">
-        <v>-19.34167807331005</v>
+        <v>-15.70597075117164</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-8.968519961478828</v>
       </c>
       <c r="E7">
-        <v>-29.84134385097805</v>
+        <v>-25.62988340197765</v>
       </c>
       <c r="F7">
-        <v>-3.650031016579241</v>
+        <v>-3.562722101314022</v>
       </c>
       <c r="G7">
-        <v>-18.98535909109998</v>
+        <v>-16.88014180085819</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-8.219856548012011</v>
       </c>
       <c r="E8">
-        <v>-31.5855490136684</v>
+        <v>-25.85908305692788</v>
       </c>
       <c r="F8">
-        <v>-3.736273305910412</v>
+        <v>-3.737213235371225</v>
       </c>
       <c r="G8">
-        <v>-18.81426513181214</v>
+        <v>-14.91055590608757</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-7.50806650809346</v>
       </c>
       <c r="E9">
-        <v>-31.8358151297023</v>
+        <v>-26.29700460736563</v>
       </c>
       <c r="F9">
-        <v>-3.717690892551603</v>
+        <v>-3.062427027067828</v>
       </c>
       <c r="G9">
-        <v>-18.60507341445836</v>
+        <v>-14.28037866523237</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-6.799222996583378</v>
       </c>
       <c r="E10">
-        <v>-32.67185520828739</v>
+        <v>-25.44935578566188</v>
       </c>
       <c r="F10">
-        <v>-3.55933376250794</v>
+        <v>-3.473782760808859</v>
       </c>
       <c r="G10">
-        <v>-17.25841466581193</v>
+        <v>-13.33516328976905</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-6.072307158769946</v>
       </c>
       <c r="E11">
-        <v>-32.85048765823096</v>
+        <v>-27.68445205925769</v>
       </c>
       <c r="F11">
-        <v>-3.261610511905605</v>
+        <v>-3.476501983865668</v>
       </c>
       <c r="G11">
-        <v>-16.44522881227305</v>
+        <v>-14.47428393855857</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-5.308690951768581</v>
       </c>
       <c r="E12">
-        <v>-32.34275288825395</v>
+        <v>-27.64939261349031</v>
       </c>
       <c r="F12">
-        <v>-3.302826458354916</v>
+        <v>-3.123764749025755</v>
       </c>
       <c r="G12">
-        <v>-16.96608025251213</v>
+        <v>-12.54448914589722</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-4.498368406165666</v>
       </c>
       <c r="E13">
-        <v>-33.42626275017321</v>
+        <v>-30.04027744989801</v>
       </c>
       <c r="F13">
-        <v>-3.41508111734718</v>
+        <v>-3.22585122418794</v>
       </c>
       <c r="G13">
-        <v>-15.37551871653267</v>
+        <v>-13.33808981202577</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-3.647486353799963</v>
       </c>
       <c r="E14">
-        <v>-34.35902424085113</v>
+        <v>-28.55399152431453</v>
       </c>
       <c r="F14">
-        <v>-3.242771538188495</v>
+        <v>-3.018304980263685</v>
       </c>
       <c r="G14">
-        <v>-15.70113569941154</v>
+        <v>-13.0600304710913</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-2.767320675903043</v>
       </c>
       <c r="E15">
-        <v>-34.82126143247307</v>
+        <v>-31.46569162787038</v>
       </c>
       <c r="F15">
-        <v>-3.024547948982347</v>
+        <v>-3.819502594737459</v>
       </c>
       <c r="G15">
-        <v>-14.35997576690584</v>
+        <v>-11.58332521729846</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-1.876650176677346</v>
       </c>
       <c r="E16">
-        <v>-35.42472814297222</v>
+        <v>-29.49931500188972</v>
       </c>
       <c r="F16">
-        <v>-3.437991007119927</v>
+        <v>-2.912963989445272</v>
       </c>
       <c r="G16">
-        <v>-14.91896138121178</v>
+        <v>-11.55464596129175</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-1.000662777244849</v>
       </c>
       <c r="E17">
-        <v>-35.113463482055</v>
+        <v>-32.79243488568963</v>
       </c>
       <c r="F17">
-        <v>-3.147375428666084</v>
+        <v>-2.774303409871929</v>
       </c>
       <c r="G17">
-        <v>-14.12922908754587</v>
+        <v>-10.79147914030572</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-0.1797519562054839</v>
       </c>
       <c r="E18">
-        <v>-35.76593054555416</v>
+        <v>-30.77534614353407</v>
       </c>
       <c r="F18">
-        <v>-3.059556560096094</v>
+        <v>-2.857313355429688</v>
       </c>
       <c r="G18">
-        <v>-14.20301287125238</v>
+        <v>-11.52012359240823</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>0.5407144260715425</v>
       </c>
       <c r="E19">
-        <v>-37.35708007949626</v>
+        <v>-32.60264201155416</v>
       </c>
       <c r="F19">
-        <v>-3.078784333615444</v>
+        <v>-2.679867817987232</v>
       </c>
       <c r="G19">
-        <v>-13.6694654888702</v>
+        <v>-11.02823942563778</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>1.114788304378275</v>
       </c>
       <c r="E20">
-        <v>-38.06565267171344</v>
+        <v>-33.56208074261126</v>
       </c>
       <c r="F20">
-        <v>-2.91465934662775</v>
+        <v>-2.687459312292892</v>
       </c>
       <c r="G20">
-        <v>-13.88475854165285</v>
+        <v>-10.90557378177116</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>1.503848161194075</v>
       </c>
       <c r="E21">
-        <v>-37.54879529084798</v>
+        <v>-34.74054364752335</v>
       </c>
       <c r="F21">
-        <v>-2.619637898317155</v>
+        <v>-3.079961818963573</v>
       </c>
       <c r="G21">
-        <v>-15.08802928662959</v>
+        <v>-10.16763000724884</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>1.682082204570204</v>
       </c>
       <c r="E22">
-        <v>-37.63453515347221</v>
+        <v>-34.27661054238553</v>
       </c>
       <c r="F22">
-        <v>-2.915212851845196</v>
+        <v>-2.809484644930459</v>
       </c>
       <c r="G22">
-        <v>-13.72117621019361</v>
+        <v>-10.2191255431122</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>1.646936212466888</v>
       </c>
       <c r="E23">
-        <v>-38.17113894524811</v>
+        <v>-33.96483642814245</v>
       </c>
       <c r="F23">
-        <v>-2.871167614777952</v>
+        <v>-3.0695069843628</v>
       </c>
       <c r="G23">
-        <v>-14.2602124770799</v>
+        <v>-10.65302550476232</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>1.418800730552823</v>
       </c>
       <c r="E24">
-        <v>-38.22764297967882</v>
+        <v>-34.64266294608456</v>
       </c>
       <c r="F24">
-        <v>-2.817819689163417</v>
+        <v>-2.485917689347025</v>
       </c>
       <c r="G24">
-        <v>-13.94049985217033</v>
+        <v>-11.1286250980251</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>1.033898408531203</v>
       </c>
       <c r="E25">
-        <v>-38.01357522062523</v>
+        <v>-33.76996939888138</v>
       </c>
       <c r="F25">
-        <v>-2.589669431279294</v>
+        <v>-2.21394074581199</v>
       </c>
       <c r="G25">
-        <v>-14.13282930581983</v>
+        <v>-11.64901637243422</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>0.5388483607509528</v>
       </c>
       <c r="E26">
-        <v>-38.4443644245009</v>
+        <v>-35.57606068736055</v>
       </c>
       <c r="F26">
-        <v>-2.84219292320203</v>
+        <v>-2.898964029152788</v>
       </c>
       <c r="G26">
-        <v>-14.21175271147605</v>
+        <v>-9.471855961805755</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-0.01508314727368545</v>
       </c>
       <c r="E27">
-        <v>-38.69597776155209</v>
+        <v>-34.11003289025039</v>
       </c>
       <c r="F27">
-        <v>-2.59694972737257</v>
+        <v>-2.463140039018217</v>
       </c>
       <c r="G27">
-        <v>-13.70198994352077</v>
+        <v>-10.64924155121093</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-0.5790101050574465</v>
       </c>
       <c r="E28">
-        <v>-38.1306294810125</v>
+        <v>-34.86560877843019</v>
       </c>
       <c r="F28">
-        <v>-2.736046617925616</v>
+        <v>-2.985711520670983</v>
       </c>
       <c r="G28">
-        <v>-13.27959909343793</v>
+        <v>-11.29598972776295</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-1.116265795403157</v>
       </c>
       <c r="E29">
-        <v>-39.54280466522345</v>
+        <v>-35.07950898394549</v>
       </c>
       <c r="F29">
-        <v>-2.846282051875694</v>
+        <v>-3.20615467371762</v>
       </c>
       <c r="G29">
-        <v>-12.8508238562826</v>
+        <v>-10.31963370568448</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-1.601272440191698</v>
       </c>
       <c r="E30">
-        <v>-37.77759870432253</v>
+        <v>-34.16714374019812</v>
       </c>
       <c r="F30">
-        <v>-2.867728597382575</v>
+        <v>-3.06467668132071</v>
       </c>
       <c r="G30">
-        <v>-14.17099161952378</v>
+        <v>-9.582702958097173</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-2.0212844052191</v>
       </c>
       <c r="E31">
-        <v>-38.15007021992742</v>
+        <v>-36.2456453826087</v>
       </c>
       <c r="F31">
-        <v>-2.897218785233973</v>
+        <v>-2.563384664200746</v>
       </c>
       <c r="G31">
-        <v>-13.72968762277508</v>
+        <v>-10.85473704447012</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-2.37676080309953</v>
       </c>
       <c r="E32">
-        <v>-38.66465430684103</v>
+        <v>-33.76924937151416</v>
       </c>
       <c r="F32">
-        <v>-3.172144589183557</v>
+        <v>-2.855554650010592</v>
       </c>
       <c r="G32">
-        <v>-13.94524717447364</v>
+        <v>-8.993511926290923</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-2.681771128646386</v>
       </c>
       <c r="E33">
-        <v>-37.96690250326517</v>
+        <v>-33.49295585112117</v>
       </c>
       <c r="F33">
-        <v>-3.140759497204336</v>
+        <v>-2.742016397373865</v>
       </c>
       <c r="G33">
-        <v>-13.23651565378985</v>
+        <v>-10.11927948964779</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-2.954721888346778</v>
       </c>
       <c r="E34">
-        <v>-37.7013641086404</v>
+        <v>-32.15983650189913</v>
       </c>
       <c r="F34">
-        <v>-2.611980680216005</v>
+        <v>-2.882910002287978</v>
       </c>
       <c r="G34">
-        <v>-13.80926982699362</v>
+        <v>-10.47163078302904</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-3.215524303967596</v>
       </c>
       <c r="E35">
-        <v>-36.88292847276013</v>
+        <v>-33.63579977098212</v>
       </c>
       <c r="F35">
-        <v>-3.007085215705754</v>
+        <v>-3.045517799008681</v>
       </c>
       <c r="G35">
-        <v>-14.06700076304419</v>
+        <v>-11.43388388111022</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-3.482071141914508</v>
       </c>
       <c r="E36">
-        <v>-36.85686257637198</v>
+        <v>-32.83892419985237</v>
       </c>
       <c r="F36">
-        <v>-2.751940690492967</v>
+        <v>-2.452092898405069</v>
       </c>
       <c r="G36">
-        <v>-13.72513562265858</v>
+        <v>-11.52555619763818</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-3.767765108111688</v>
       </c>
       <c r="E37">
-        <v>-36.395191444001</v>
+        <v>-33.17718083009231</v>
       </c>
       <c r="F37">
-        <v>-2.665616048454193</v>
+        <v>-2.418941974330133</v>
       </c>
       <c r="G37">
-        <v>-14.1685699554618</v>
+        <v>-9.464821052534804</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-4.077381017296875</v>
       </c>
       <c r="E38">
-        <v>-36.44900103639714</v>
+        <v>-33.59181017447162</v>
       </c>
       <c r="F38">
-        <v>-2.556690339296183</v>
+        <v>-2.631020784584376</v>
       </c>
       <c r="G38">
-        <v>-13.90042900896299</v>
+        <v>-10.80134125546721</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.408232854927869</v>
       </c>
       <c r="E39">
-        <v>-36.60031773112645</v>
+        <v>-32.2987949910615</v>
       </c>
       <c r="F39">
-        <v>-2.722028445015104</v>
+        <v>-2.394501432790114</v>
       </c>
       <c r="G39">
-        <v>-13.54109908558496</v>
+        <v>-10.63648270870258</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.752550605773671</v>
       </c>
       <c r="E40">
-        <v>-35.65164091854857</v>
+        <v>-30.57611366532961</v>
       </c>
       <c r="F40">
-        <v>-2.781000110335365</v>
+        <v>-1.861041972968702</v>
       </c>
       <c r="G40">
-        <v>-14.05402507980302</v>
+        <v>-10.71519092889876</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-5.102143088192554</v>
       </c>
       <c r="E41">
-        <v>-35.3322000978105</v>
+        <v>-30.4938675204023</v>
       </c>
       <c r="F41">
-        <v>-2.759817251863404</v>
+        <v>-1.923356841476456</v>
       </c>
       <c r="G41">
-        <v>-14.31667879707048</v>
+        <v>-11.46074564761586</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-5.446898280493999</v>
       </c>
       <c r="E42">
-        <v>-34.84525555200271</v>
+        <v>-30.65364566881494</v>
       </c>
       <c r="F42">
-        <v>-2.475958554697784</v>
+        <v>-2.442874938124254</v>
       </c>
       <c r="G42">
-        <v>-14.24821837059113</v>
+        <v>-11.72678770824277</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-5.776945739128121</v>
       </c>
       <c r="E43">
-        <v>-34.32021521860539</v>
+        <v>-30.83031955375019</v>
       </c>
       <c r="F43">
-        <v>-2.405886694616208</v>
+        <v>-1.774131359741216</v>
       </c>
       <c r="G43">
-        <v>-14.76860964500024</v>
+        <v>-10.71424411287452</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-6.086439648848669</v>
       </c>
       <c r="E44">
-        <v>-34.26261529346483</v>
+        <v>-28.1865783141762</v>
       </c>
       <c r="F44">
-        <v>-2.498218333192244</v>
+        <v>-2.263365040021024</v>
       </c>
       <c r="G44">
-        <v>-14.77104951706268</v>
+        <v>-12.25280359952311</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-6.374850041694772</v>
       </c>
       <c r="E45">
-        <v>-33.61194829838372</v>
+        <v>-29.21587328527563</v>
       </c>
       <c r="F45">
-        <v>-2.353991027326131</v>
+        <v>-2.454812121461879</v>
       </c>
       <c r="G45">
-        <v>-14.74048490537136</v>
+        <v>-11.40294021195465</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-6.643109029486834</v>
       </c>
       <c r="E46">
-        <v>-33.39759298123065</v>
+        <v>-28.3335227672511</v>
       </c>
       <c r="F46">
-        <v>-2.1801484208413</v>
+        <v>-2.231963319129691</v>
       </c>
       <c r="G46">
-        <v>-15.36819082398149</v>
+        <v>-11.37156948242452</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-6.894082846229582</v>
       </c>
       <c r="E47">
-        <v>-32.85139335303249</v>
+        <v>-28.28386352128298</v>
       </c>
       <c r="F47">
-        <v>-2.276516133942833</v>
+        <v>-2.124012380962633</v>
       </c>
       <c r="G47">
-        <v>-15.07096342437465</v>
+        <v>-12.18256044427086</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-7.134511490501014</v>
       </c>
       <c r="E48">
-        <v>-33.43685711511416</v>
+        <v>-27.65625778008594</v>
       </c>
       <c r="F48">
-        <v>-2.105623971578466</v>
+        <v>-1.922010691448332</v>
       </c>
       <c r="G48">
-        <v>-15.72390397635787</v>
+        <v>-11.71075142565054</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-7.372148163548011</v>
       </c>
       <c r="E49">
-        <v>-31.78834087244289</v>
+        <v>-27.61388937727018</v>
       </c>
       <c r="F49">
-        <v>-1.963893378088044</v>
+        <v>-2.333765519080054</v>
       </c>
       <c r="G49">
-        <v>-15.67451725800303</v>
+        <v>-12.66565511263454</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-7.610980427976344</v>
       </c>
       <c r="E50">
-        <v>-32.67695427002003</v>
+        <v>-25.73171066851413</v>
       </c>
       <c r="F50">
-        <v>-2.349770451061485</v>
+        <v>-2.340096383477023</v>
       </c>
       <c r="G50">
-        <v>-15.20989046793016</v>
+        <v>-13.07159751720552</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-7.852171177456455</v>
       </c>
       <c r="E51">
-        <v>-31.76962468936919</v>
+        <v>-25.52817387576538</v>
       </c>
       <c r="F51">
-        <v>-2.283907289450189</v>
+        <v>-1.883596320763433</v>
       </c>
       <c r="G51">
-        <v>-16.15800257074035</v>
+        <v>-12.97656830750074</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-8.096955458356778</v>
       </c>
       <c r="E52">
-        <v>-30.76767943703909</v>
+        <v>-24.61213603959779</v>
       </c>
       <c r="F52">
-        <v>-2.274662406168811</v>
+        <v>-1.901596722198318</v>
       </c>
       <c r="G52">
-        <v>-15.66467500611477</v>
+        <v>-12.88417760259076</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-8.346124559804496</v>
       </c>
       <c r="E53">
-        <v>-30.82432385416403</v>
+        <v>-26.96019962578895</v>
       </c>
       <c r="F53">
-        <v>-2.154009354706972</v>
+        <v>-2.221365159143569</v>
       </c>
       <c r="G53">
-        <v>-15.89600599676243</v>
+        <v>-13.1862350881394</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-8.598840873140722</v>
       </c>
       <c r="E54">
-        <v>-30.59307506472534</v>
+        <v>-24.57395194676511</v>
       </c>
       <c r="F54">
-        <v>-2.087845288971743</v>
+        <v>-2.35523106905792</v>
       </c>
       <c r="G54">
-        <v>-17.07512631203018</v>
+        <v>-13.62795786889881</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-8.850411312344148</v>
       </c>
       <c r="E55">
-        <v>-31.21674103353571</v>
+        <v>-24.70795402112608</v>
       </c>
       <c r="F55">
-        <v>-2.445613957505007</v>
+        <v>-1.634989333569579</v>
       </c>
       <c r="G55">
-        <v>-16.26319515525069</v>
+        <v>-12.99578933490175</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-9.102153056747898</v>
       </c>
       <c r="E56">
-        <v>-29.5228585382556</v>
+        <v>-25.59394996072679</v>
       </c>
       <c r="F56">
-        <v>-2.429286741369784</v>
+        <v>-1.69854503566208</v>
       </c>
       <c r="G56">
-        <v>-16.60920509865146</v>
+        <v>-13.70716101565311</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-9.356440207500741</v>
       </c>
       <c r="E57">
-        <v>-29.73467338149037</v>
+        <v>-22.32895190051451</v>
       </c>
       <c r="F57">
-        <v>-2.331020164875639</v>
+        <v>-2.038239660435391</v>
       </c>
       <c r="G57">
-        <v>-16.6378992521131</v>
+        <v>-14.39988935920007</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-9.614103954090854</v>
       </c>
       <c r="E58">
-        <v>-29.62556206451256</v>
+        <v>-23.96921952778081</v>
       </c>
       <c r="F58">
-        <v>-2.020879868043302</v>
+        <v>-1.764510346304921</v>
       </c>
       <c r="G58">
-        <v>-17.0375003067036</v>
+        <v>-13.18312317533248</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-9.871314212569562</v>
       </c>
       <c r="E59">
-        <v>-29.26749788896307</v>
+        <v>-23.27824684979444</v>
       </c>
       <c r="F59">
-        <v>-2.39429792657998</v>
+        <v>-2.002687838192649</v>
       </c>
       <c r="G59">
-        <v>-17.44131734103836</v>
+        <v>-14.07040896967687</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-10.1297418705077</v>
       </c>
       <c r="E60">
-        <v>-28.48338808606094</v>
+        <v>-24.35657160897491</v>
       </c>
       <c r="F60">
-        <v>-2.115238650191099</v>
+        <v>-1.965573690064325</v>
       </c>
       <c r="G60">
-        <v>-16.87742384297045</v>
+        <v>-13.81711416464892</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-10.38736533425912</v>
       </c>
       <c r="E61">
-        <v>-28.93932843457521</v>
+        <v>-24.3472972942072</v>
       </c>
       <c r="F61">
-        <v>-2.418340166082266</v>
+        <v>-2.073732093706304</v>
       </c>
       <c r="G61">
-        <v>-17.51666535751217</v>
+        <v>-13.44847664248723</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-10.63924778014801</v>
       </c>
       <c r="E62">
-        <v>-29.14460416134291</v>
+        <v>-22.55263134564938</v>
       </c>
       <c r="F62">
-        <v>-1.873889787207704</v>
+        <v>-2.810430117361976</v>
       </c>
       <c r="G62">
-        <v>-17.44498211495033</v>
+        <v>-14.64326908033789</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-10.87729786829968</v>
       </c>
       <c r="E63">
-        <v>-29.16036777936361</v>
+        <v>-22.92277069714033</v>
       </c>
       <c r="F63">
-        <v>-2.716475972075573</v>
+        <v>-2.072659132948594</v>
       </c>
       <c r="G63">
-        <v>-17.21786710404694</v>
+        <v>-15.42466707560869</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-11.10126812001183</v>
       </c>
       <c r="E64">
-        <v>-27.75206670466622</v>
+        <v>-23.64979002822776</v>
       </c>
       <c r="F64">
-        <v>-2.479449042535413</v>
+        <v>-2.03894124215593</v>
       </c>
       <c r="G64">
-        <v>-17.72020431835764</v>
+        <v>-15.43308579291506</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-11.30934583952913</v>
       </c>
       <c r="E65">
-        <v>-27.54926805318072</v>
+        <v>-22.53223509871884</v>
       </c>
       <c r="F65">
-        <v>-2.430917166609729</v>
+        <v>-1.76728895833356</v>
       </c>
       <c r="G65">
-        <v>-17.77365804190748</v>
+        <v>-14.21738063889281</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-11.49797483337142</v>
       </c>
       <c r="E66">
-        <v>-29.74752971919815</v>
+        <v>-23.59782126051573</v>
       </c>
       <c r="F66">
-        <v>-2.615366643463215</v>
+        <v>-2.462285629676838</v>
       </c>
       <c r="G66">
-        <v>-17.76535519369499</v>
+        <v>-15.66789285637894</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-11.66091195969616</v>
       </c>
       <c r="E67">
-        <v>-28.77373119706272</v>
+        <v>-23.6897855106635</v>
       </c>
       <c r="F67">
-        <v>-2.632313880464332</v>
+        <v>-2.914664097745496</v>
       </c>
       <c r="G67">
-        <v>-17.87724997764959</v>
+        <v>-14.97500064082779</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-11.79744663301914</v>
       </c>
       <c r="E68">
-        <v>-27.70283766372884</v>
+        <v>-21.06771754769023</v>
       </c>
       <c r="F68">
-        <v>-2.540249888188006</v>
+        <v>-2.507867061482058</v>
       </c>
       <c r="G68">
-        <v>-17.51370572980006</v>
+        <v>-14.80287710187724</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-11.90315951472558</v>
       </c>
       <c r="E69">
-        <v>-28.26216760231224</v>
+        <v>-22.84205064795361</v>
       </c>
       <c r="F69">
-        <v>-2.753293967197709</v>
+        <v>-2.549368866849107</v>
       </c>
       <c r="G69">
-        <v>-17.59817595450734</v>
+        <v>-15.82725589754838</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-11.97041735807207</v>
       </c>
       <c r="E70">
-        <v>-28.40683876143528</v>
+        <v>-22.28989381219836</v>
       </c>
       <c r="F70">
-        <v>-2.697494464826073</v>
+        <v>-2.90268573805407</v>
       </c>
       <c r="G70">
-        <v>-17.73769227516884</v>
+        <v>-14.55822447597956</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-11.98958236953343</v>
       </c>
       <c r="E71">
-        <v>-28.61712298045546</v>
+        <v>-21.43774368733098</v>
       </c>
       <c r="F71">
-        <v>-2.986486744716591</v>
+        <v>-2.246905584441862</v>
       </c>
       <c r="G71">
-        <v>-18.66400278033015</v>
+        <v>-15.1157269658839</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-11.9590374021212</v>
       </c>
       <c r="E72">
-        <v>-28.58004836375466</v>
+        <v>-22.21314070624235</v>
       </c>
       <c r="F72">
-        <v>-2.514545549327466</v>
+        <v>-1.983984271331309</v>
       </c>
       <c r="G72">
-        <v>-18.39223016537477</v>
+        <v>-15.05203703552663</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-11.87826766576559</v>
       </c>
       <c r="E73">
-        <v>-28.00865457041483</v>
+        <v>-23.50365617200024</v>
       </c>
       <c r="F73">
-        <v>-2.941028841972775</v>
+        <v>-2.439953000710268</v>
       </c>
       <c r="G73">
-        <v>-18.11523019901287</v>
+        <v>-14.81621694512773</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-11.74866208687449</v>
       </c>
       <c r="E74">
-        <v>-28.36692932000568</v>
+        <v>-22.24916471697337</v>
       </c>
       <c r="F74">
-        <v>-2.888128313279351</v>
+        <v>-2.996688186370894</v>
       </c>
       <c r="G74">
-        <v>-18.71166967027735</v>
+        <v>-14.82853382980659</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-11.57265249622838</v>
       </c>
       <c r="E75">
-        <v>-29.17974511964243</v>
+        <v>-25.08360905395837</v>
       </c>
       <c r="F75">
-        <v>-2.816188472070514</v>
+        <v>-2.402356614130694</v>
       </c>
       <c r="G75">
-        <v>-17.91016507667379</v>
+        <v>-14.45462757441914</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-11.36032177326133</v>
       </c>
       <c r="E76">
-        <v>-29.34350832518182</v>
+        <v>-23.15051218346008</v>
       </c>
       <c r="F76">
-        <v>-2.712731299438516</v>
+        <v>-2.454380561599922</v>
       </c>
       <c r="G76">
-        <v>-17.9057488089244</v>
+        <v>-14.04149632020964</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-11.11895426561466</v>
       </c>
       <c r="E77">
-        <v>-29.75803804313295</v>
+        <v>-23.92302456442857</v>
       </c>
       <c r="F77">
-        <v>-3.319456954172946</v>
+        <v>-2.602917923114903</v>
       </c>
       <c r="G77">
-        <v>-17.9447917277418</v>
+        <v>-14.60999478712268</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-10.85340385896607</v>
       </c>
       <c r="E78">
-        <v>-29.14738011590961</v>
+        <v>-21.80022086080095</v>
       </c>
       <c r="F78">
-        <v>-3.016681681700359</v>
+        <v>-2.701245472286792</v>
       </c>
       <c r="G78">
-        <v>-17.59118573760117</v>
+        <v>-15.59554088361817</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-10.56507997403814</v>
       </c>
       <c r="E79">
-        <v>-30.41220781285898</v>
+        <v>-25.88759885775417</v>
       </c>
       <c r="F79">
-        <v>-3.067590700205118</v>
+        <v>-3.053589948059676</v>
       </c>
       <c r="G79">
-        <v>-17.90579846710749</v>
+        <v>-14.12427485614635</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-10.26107671071695</v>
       </c>
       <c r="E80">
-        <v>-31.06002186931526</v>
+        <v>-24.12252648683648</v>
       </c>
       <c r="F80">
-        <v>-3.036887393622493</v>
+        <v>-3.213517322518497</v>
       </c>
       <c r="G80">
-        <v>-18.2431281601043</v>
+        <v>-14.56641973146202</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-9.943547515336711</v>
       </c>
       <c r="E81">
-        <v>-29.98496440413132</v>
+        <v>-24.25699952249425</v>
       </c>
       <c r="F81">
-        <v>-2.621237441291749</v>
+        <v>-2.570053649810661</v>
       </c>
       <c r="G81">
-        <v>-17.84780267507777</v>
+        <v>-14.8995913792615</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-9.612520355680404</v>
       </c>
       <c r="E82">
-        <v>-30.74986442029291</v>
+        <v>-24.90602494574758</v>
       </c>
       <c r="F82">
-        <v>-2.951809128139171</v>
+        <v>-2.652987577484479</v>
       </c>
       <c r="G82">
-        <v>-17.63531696491242</v>
+        <v>-14.30562323024209</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-9.267227775957137</v>
       </c>
       <c r="E83">
-        <v>-30.62730353551231</v>
+        <v>-25.82794979812514</v>
       </c>
       <c r="F83">
-        <v>-3.042294165617804</v>
+        <v>-2.820129524241085</v>
       </c>
       <c r="G83">
-        <v>-16.98080555907081</v>
+        <v>-13.3522125992963</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-8.914631532039719</v>
       </c>
       <c r="E84">
-        <v>-33.09967373321403</v>
+        <v>-28.11468426083043</v>
       </c>
       <c r="F84">
-        <v>-2.946099076461054</v>
+        <v>-2.662504858183312</v>
       </c>
       <c r="G84">
-        <v>-17.9244964283133</v>
+        <v>-14.13789940631322</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-8.55902574233531</v>
       </c>
       <c r="E85">
-        <v>-33.6808286522774</v>
+        <v>-28.10402876149038</v>
       </c>
       <c r="F85">
-        <v>-2.835898484041115</v>
+        <v>-2.343742074494364</v>
       </c>
       <c r="G85">
-        <v>-17.31495050725884</v>
+        <v>-15.36861126326498</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-8.20414021721156</v>
       </c>
       <c r="E86">
-        <v>-33.79593114036736</v>
+        <v>-30.26024128210958</v>
       </c>
       <c r="F86">
-        <v>-3.100939587519485</v>
+        <v>-2.3717744610506</v>
       </c>
       <c r="G86">
-        <v>-17.34233202941415</v>
+        <v>-13.79077380906571</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-7.855099566377946</v>
       </c>
       <c r="E87">
-        <v>-34.5184129404991</v>
+        <v>-30.43873787783292</v>
       </c>
       <c r="F87">
-        <v>-3.121324258210063</v>
+        <v>-2.868315360424246</v>
       </c>
       <c r="G87">
-        <v>-17.00823673940921</v>
+        <v>-14.09374334991042</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-7.524793148105737</v>
       </c>
       <c r="E88">
-        <v>-35.44969135593951</v>
+        <v>-29.11037342631893</v>
       </c>
       <c r="F88">
-        <v>-2.850851043441737</v>
+        <v>-3.427255856572121</v>
       </c>
       <c r="G88">
-        <v>-16.67523723997777</v>
+        <v>-12.91528017793221</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-7.222416200723534</v>
       </c>
       <c r="E89">
-        <v>-36.42789381904739</v>
+        <v>-32.50263519156876</v>
       </c>
       <c r="F89">
-        <v>-3.098487218909426</v>
+        <v>-3.091307488141782</v>
       </c>
       <c r="G89">
-        <v>-17.3287554821576</v>
+        <v>-11.84506356872432</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-6.953448633833268</v>
       </c>
       <c r="E90">
-        <v>-37.80572732062117</v>
+        <v>-32.15812473872423</v>
       </c>
       <c r="F90">
-        <v>-3.087919149335699</v>
+        <v>-2.342107689989631</v>
       </c>
       <c r="G90">
-        <v>-16.30580518688665</v>
+        <v>-13.59944414016907</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-6.723751281312408</v>
       </c>
       <c r="E91">
-        <v>-39.06817756871652</v>
+        <v>-32.68400736828697</v>
       </c>
       <c r="F91">
-        <v>-2.870253816464743</v>
+        <v>-2.933337574194443</v>
       </c>
       <c r="G91">
-        <v>-16.23430733487501</v>
+        <v>-12.66518832571351</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-6.537944176774698</v>
       </c>
       <c r="E92">
-        <v>-39.37620210648125</v>
+        <v>-34.55745970763024</v>
       </c>
       <c r="F92">
-        <v>-2.789971012493372</v>
+        <v>-2.952724510158295</v>
       </c>
       <c r="G92">
-        <v>-16.69061472400768</v>
+        <v>-14.29359105247961</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.393895599723378</v>
       </c>
       <c r="E93">
-        <v>-41.22693056325403</v>
+        <v>-36.84640859412527</v>
       </c>
       <c r="F93">
-        <v>-3.000789984691882</v>
+        <v>-2.737213017332337</v>
       </c>
       <c r="G93">
-        <v>-16.69669288561779</v>
+        <v>-14.07782790223038</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.2819964581132</v>
       </c>
       <c r="E94">
-        <v>-42.1616687328363</v>
+        <v>-38.37881249900287</v>
       </c>
       <c r="F94">
-        <v>-3.339358594559316</v>
+        <v>-2.971457375579071</v>
       </c>
       <c r="G94">
-        <v>-16.15844618384261</v>
+        <v>-13.84606323011708</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-6.191642650061238</v>
       </c>
       <c r="E95">
-        <v>-43.76761279136145</v>
+        <v>-39.05696506707353</v>
       </c>
       <c r="F95">
-        <v>-2.98138562796296</v>
+        <v>-2.467862650058058</v>
       </c>
       <c r="G95">
-        <v>-15.6803570603343</v>
+        <v>-13.49106018975887</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-6.106405478113732</v>
       </c>
       <c r="E96">
-        <v>-44.89276197178124</v>
+        <v>-42.15676213124898</v>
       </c>
       <c r="F96">
-        <v>-2.859751470686507</v>
+        <v>-2.982814130698687</v>
       </c>
       <c r="G96">
-        <v>-15.98406981865258</v>
+        <v>-13.16210452170365</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-6.010073992886497</v>
       </c>
       <c r="E97">
-        <v>-46.80616224458317</v>
+        <v>-44.01121525789307</v>
       </c>
       <c r="F97">
-        <v>-3.278877657501641</v>
+        <v>-2.585591388547038</v>
       </c>
       <c r="G97">
-        <v>-16.40614451163642</v>
+        <v>-12.9548246443988</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-5.879663379501417</v>
       </c>
       <c r="E98">
-        <v>-49.35029403776593</v>
+        <v>-45.01359750796491</v>
       </c>
       <c r="F98">
-        <v>-3.365280692983229</v>
+        <v>-3.162833982106689</v>
       </c>
       <c r="G98">
-        <v>-15.75619172700239</v>
+        <v>-13.74916190690984</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-5.712487914217352</v>
       </c>
       <c r="E99">
-        <v>-49.95907151615759</v>
+        <v>-49.07686364506429</v>
       </c>
       <c r="F99">
-        <v>-3.189571689077053</v>
+        <v>-2.604667126298506</v>
       </c>
       <c r="G99">
-        <v>-16.04678479334853</v>
+        <v>-13.29704897897542</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-5.496677640657905</v>
       </c>
       <c r="E100">
-        <v>-52.80994515684241</v>
+        <v>-48.57262259278421</v>
       </c>
       <c r="F100">
-        <v>-3.64372865888875</v>
+        <v>-3.25239571903662</v>
       </c>
       <c r="G100">
-        <v>-16.3293580631258</v>
+        <v>-13.94296289805155</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-5.255986846024574</v>
       </c>
       <c r="E101">
-        <v>-52.60653629348437</v>
+        <v>-51.91399449925434</v>
       </c>
       <c r="F101">
-        <v>-3.864605747356217</v>
+        <v>-3.479808761817106</v>
       </c>
       <c r="G101">
-        <v>-15.33445802020909</v>
+        <v>-12.9535600160028</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.972356820827913</v>
       </c>
       <c r="E102">
-        <v>-55.23121378960457</v>
+        <v>-53.09355216275779</v>
       </c>
       <c r="F102">
-        <v>-3.494668674421674</v>
+        <v>-3.283567802570215</v>
       </c>
       <c r="G102">
-        <v>-16.11231538702564</v>
+        <v>-13.62639529140428</v>
       </c>
     </row>
   </sheetData>
